--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/CALIFORNIA_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/CALIFORNIA_2019.xlsx
@@ -1705,7 +1705,7 @@
         <v>23</v>
       </c>
       <c r="D75">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="76">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C208">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C263">
@@ -5413,7 +5413,7 @@
         <v>23</v>
       </c>
       <c r="D281">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="282">
@@ -6673,7 +6673,7 @@
         <v>23</v>
       </c>
       <c r="D351">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="352">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C429">
@@ -8095,7 +8095,7 @@
         <v>225</v>
       </c>
       <c r="D430">
-        <v>0.0009177567577489263</v>
+        <v>0.0009177567577489264</v>
       </c>
     </row>
     <row r="431">
@@ -12577,7 +12577,7 @@
         <v>225</v>
       </c>
       <c r="D679">
-        <v>0.0009177567577489263</v>
+        <v>0.0009177567577489264</v>
       </c>
     </row>
     <row r="680">
@@ -13783,7 +13783,7 @@
         <v>238</v>
       </c>
       <c r="D746">
-        <v>0.0009707827037521975</v>
+        <v>0.0009707827037521976</v>
       </c>
     </row>
     <row r="747">
@@ -13909,7 +13909,7 @@
         <v>23</v>
       </c>
       <c r="D753">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="754">
@@ -16393,7 +16393,7 @@
         <v>243</v>
       </c>
       <c r="D891">
-        <v>0.0009911772983688403</v>
+        <v>0.0009911772983688405</v>
       </c>
     </row>
     <row r="892">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="B924" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C924">
@@ -17203,7 +17203,7 @@
         <v>234</v>
       </c>
       <c r="D936">
-        <v>0.0009544670280588833</v>
+        <v>0.0009544670280588832</v>
       </c>
     </row>
     <row r="937">
@@ -17563,7 +17563,7 @@
         <v>23</v>
       </c>
       <c r="D956">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="957">
@@ -17887,7 +17887,7 @@
         <v>23</v>
       </c>
       <c r="D974">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="975">
@@ -19273,7 +19273,7 @@
         <v>23</v>
       </c>
       <c r="D1051">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1052">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>San Bartolome Yucane</t>
+          <t>San Bartolome Yucuane</t>
         </is>
       </c>
       <c r="C1062">
@@ -21012,7 +21012,7 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1148">
@@ -21030,7 +21030,7 @@
       </c>
       <c r="B1149" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1149">
@@ -21091,7 +21091,7 @@
         <v>23</v>
       </c>
       <c r="D1152">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1153">
@@ -21325,7 +21325,7 @@
         <v>23</v>
       </c>
       <c r="D1165">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1166">
@@ -22081,7 +22081,7 @@
         <v>23</v>
       </c>
       <c r="D1207">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1208">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1249">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="B1250" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1250">
@@ -23082,7 +23082,7 @@
       </c>
       <c r="B1263" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1263">
@@ -25465,7 +25465,7 @@
         <v>233</v>
       </c>
       <c r="D1395">
-        <v>0.0009503881091355547</v>
+        <v>0.0009503881091355548</v>
       </c>
     </row>
     <row r="1396">
@@ -25519,7 +25519,7 @@
         <v>23</v>
       </c>
       <c r="D1398">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1399">
@@ -26214,7 +26214,7 @@
       </c>
       <c r="B1437" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1437">
@@ -26347,7 +26347,7 @@
         <v>23</v>
       </c>
       <c r="D1444">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1445">
@@ -26797,7 +26797,7 @@
         <v>23</v>
       </c>
       <c r="D1469">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1470">
@@ -26941,7 +26941,7 @@
         <v>23</v>
       </c>
       <c r="D1477">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1478">
@@ -27697,7 +27697,7 @@
         <v>23</v>
       </c>
       <c r="D1519">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1520">
@@ -28957,7 +28957,7 @@
         <v>23</v>
       </c>
       <c r="D1589">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1590">
@@ -31387,7 +31387,7 @@
         <v>23</v>
       </c>
       <c r="D1724">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1725">
@@ -34789,7 +34789,7 @@
         <v>233</v>
       </c>
       <c r="D1913">
-        <v>0.0009503881091355547</v>
+        <v>0.0009503881091355548</v>
       </c>
     </row>
     <row r="1914">
@@ -34933,7 +34933,7 @@
         <v>23</v>
       </c>
       <c r="D1921">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1922">
@@ -35041,7 +35041,7 @@
         <v>23</v>
       </c>
       <c r="D1927">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="1928">
@@ -35610,7 +35610,7 @@
       </c>
       <c r="B1959" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1959">
@@ -37399,7 +37399,7 @@
         <v>23</v>
       </c>
       <c r="D2058">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="2059">
@@ -37417,7 +37417,7 @@
         <v>242</v>
       </c>
       <c r="D2059">
-        <v>0.0009870983794455117</v>
+        <v>0.0009870983794455115</v>
       </c>
     </row>
     <row r="2060">
@@ -37453,7 +37453,7 @@
         <v>233</v>
       </c>
       <c r="D2061">
-        <v>0.0009503881091355547</v>
+        <v>0.0009503881091355548</v>
       </c>
     </row>
     <row r="2062">
@@ -41269,7 +41269,7 @@
         <v>23</v>
       </c>
       <c r="D2273">
-        <v>9.381513523655691E-05</v>
+        <v>9.381513523655692E-05</v>
       </c>
     </row>
     <row r="2274">
